--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70268,13 +70268,13 @@
         <v>46276.5625</v>
       </c>
       <c r="B2689" t="n">
-        <v>4673001</v>
+        <v>4679100</v>
       </c>
       <c r="C2689" t="n">
         <v>341.140014648438</v>
       </c>
       <c r="D2689" t="n">
-        <v>327.053009033203</v>
+        <v>327.049987792969</v>
       </c>
       <c r="E2689" t="n">
         <v>338.489990234375</v>
@@ -70286,6 +70286,32 @@
         <v>330.649993896484</v>
       </c>
       <c r="H2689" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B2690" t="n">
+        <v>11850739</v>
+      </c>
+      <c r="C2690" t="n">
+        <v>378.600006103516</v>
+      </c>
+      <c r="D2690" t="n">
+        <v>340.250091552734</v>
+      </c>
+      <c r="E2690" t="n">
+        <v>346.484985351562</v>
+      </c>
+      <c r="F2690" t="n">
+        <v>373.940002441406</v>
+      </c>
+      <c r="G2690" t="n">
+        <v>373.940002441406</v>
+      </c>
+      <c r="H2690" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70294,16 +70294,16 @@
         <v>46279.5625</v>
       </c>
       <c r="B2690" t="n">
-        <v>11850739</v>
+        <v>12027300</v>
       </c>
       <c r="C2690" t="n">
         <v>378.600006103516</v>
       </c>
       <c r="D2690" t="n">
-        <v>340.250091552734</v>
+        <v>340.25</v>
       </c>
       <c r="E2690" t="n">
-        <v>346.484985351562</v>
+        <v>346.489990234375</v>
       </c>
       <c r="F2690" t="n">
         <v>373.940002441406</v>
@@ -70312,6 +70312,32 @@
         <v>373.940002441406</v>
       </c>
       <c r="H2690" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>6471952</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>380.443115234375</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>366.799987792969</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>368.429992675781</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>375.089996337891</v>
+      </c>
+      <c r="G2691" t="n">
+        <v>375.089996337891</v>
+      </c>
+      <c r="H2691" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70320,10 +70320,10 @@
         <v>46280.5625</v>
       </c>
       <c r="B2691" t="n">
-        <v>6471952</v>
+        <v>6476400</v>
       </c>
       <c r="C2691" t="n">
-        <v>380.443115234375</v>
+        <v>380.440002441406</v>
       </c>
       <c r="D2691" t="n">
         <v>366.799987792969</v>
@@ -70338,6 +70338,32 @@
         <v>375.089996337891</v>
       </c>
       <c r="H2691" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B2692" t="n">
+        <v>5240113</v>
+      </c>
+      <c r="C2692" t="n">
+        <v>381.959991455078</v>
+      </c>
+      <c r="D2692" t="n">
+        <v>367.385101318359</v>
+      </c>
+      <c r="E2692" t="n">
+        <v>367.510009765625</v>
+      </c>
+      <c r="F2692" t="n">
+        <v>375.649993896484</v>
+      </c>
+      <c r="G2692" t="n">
+        <v>375.649993896484</v>
+      </c>
+      <c r="H2692" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70346,13 +70346,13 @@
         <v>46281.5625</v>
       </c>
       <c r="B2692" t="n">
-        <v>5240113</v>
+        <v>5242700</v>
       </c>
       <c r="C2692" t="n">
         <v>381.959991455078</v>
       </c>
       <c r="D2692" t="n">
-        <v>367.385101318359</v>
+        <v>367.299987792969</v>
       </c>
       <c r="E2692" t="n">
         <v>367.510009765625</v>
@@ -70364,6 +70364,32 @@
         <v>375.649993896484</v>
       </c>
       <c r="H2692" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>6288419</v>
+      </c>
+      <c r="C2693" t="n">
+        <v>383.119995117188</v>
+      </c>
+      <c r="D2693" t="n">
+        <v>360.660003662109</v>
+      </c>
+      <c r="E2693" t="n">
+        <v>365.359985351562</v>
+      </c>
+      <c r="F2693" t="n">
+        <v>375.059997558594</v>
+      </c>
+      <c r="G2693" t="n">
+        <v>375.059997558594</v>
+      </c>
+      <c r="H2693" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70372,7 +70372,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B2693" t="n">
-        <v>6288419</v>
+        <v>6290400</v>
       </c>
       <c r="C2693" t="n">
         <v>383.119995117188</v>
@@ -70381,7 +70381,7 @@
         <v>360.660003662109</v>
       </c>
       <c r="E2693" t="n">
-        <v>365.359985351562</v>
+        <v>365.470001220703</v>
       </c>
       <c r="F2693" t="n">
         <v>375.059997558594</v>
@@ -70390,6 +70390,32 @@
         <v>375.059997558594</v>
       </c>
       <c r="H2693" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B2694" t="n">
+        <v>13370476</v>
+      </c>
+      <c r="C2694" t="n">
+        <v>376.010009765625</v>
+      </c>
+      <c r="D2694" t="n">
+        <v>356</v>
+      </c>
+      <c r="E2694" t="n">
+        <v>375.075012207031</v>
+      </c>
+      <c r="F2694" t="n">
+        <v>363.579986572266</v>
+      </c>
+      <c r="G2694" t="n">
+        <v>363.579986572266</v>
+      </c>
+      <c r="H2694" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70398,7 +70398,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B2694" t="n">
-        <v>13370476</v>
+        <v>13790700</v>
       </c>
       <c r="C2694" t="n">
         <v>376.010009765625</v>
@@ -70407,7 +70407,7 @@
         <v>356</v>
       </c>
       <c r="E2694" t="n">
-        <v>375.075012207031</v>
+        <v>375.079986572266</v>
       </c>
       <c r="F2694" t="n">
         <v>363.579986572266</v>
@@ -70416,6 +70416,32 @@
         <v>363.579986572266</v>
       </c>
       <c r="H2694" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B2695" t="n">
+        <v>5136650</v>
+      </c>
+      <c r="C2695" t="n">
+        <v>374.559997558594</v>
+      </c>
+      <c r="D2695" t="n">
+        <v>357.589996337891</v>
+      </c>
+      <c r="E2695" t="n">
+        <v>364.260009765625</v>
+      </c>
+      <c r="F2695" t="n">
+        <v>371.760009765625</v>
+      </c>
+      <c r="G2695" t="n">
+        <v>371.760009765625</v>
+      </c>
+      <c r="H2695" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70398,7 +70398,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B2694" t="n">
-        <v>13790700</v>
+        <v>13800800</v>
       </c>
       <c r="C2694" t="n">
         <v>376.010009765625</v>
@@ -70424,7 +70424,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B2695" t="n">
-        <v>5136650</v>
+        <v>5382300</v>
       </c>
       <c r="C2695" t="n">
         <v>374.559997558594</v>
@@ -70433,7 +70433,7 @@
         <v>357.589996337891</v>
       </c>
       <c r="E2695" t="n">
-        <v>364.260009765625</v>
+        <v>364.089996337891</v>
       </c>
       <c r="F2695" t="n">
         <v>371.760009765625</v>
@@ -70442,6 +70442,32 @@
         <v>371.760009765625</v>
       </c>
       <c r="H2695" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>7925297</v>
+      </c>
+      <c r="C2696" t="n">
+        <v>377.910003662109</v>
+      </c>
+      <c r="D2696" t="n">
+        <v>363.579986572266</v>
+      </c>
+      <c r="E2696" t="n">
+        <v>374.799987792969</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>374.570007324219</v>
+      </c>
+      <c r="G2696" t="n">
+        <v>374.570007324219</v>
+      </c>
+      <c r="H2696" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -62362,13 +62362,13 @@
         <v>46288.5625</v>
       </c>
       <c r="B2696" t="n">
-        <v>6198749</v>
+        <v>6272700</v>
       </c>
       <c r="C2696" t="n">
         <v>393.519989013672</v>
       </c>
       <c r="D2696" t="n">
-        <v>374.220001220703</v>
+        <v>374.200012207031</v>
       </c>
       <c r="E2696" t="n">
         <v>379.799987792969</v>
@@ -62377,6 +62377,29 @@
         <v>393.299987792969</v>
       </c>
       <c r="G2696" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B2697" t="n">
+        <v>3965336</v>
+      </c>
+      <c r="C2697" t="n">
+        <v>396.299987792969</v>
+      </c>
+      <c r="D2697" t="n">
+        <v>387.790008544922</v>
+      </c>
+      <c r="E2697" t="n">
+        <v>392.440002441406</v>
+      </c>
+      <c r="F2697" t="n">
+        <v>389.920013427734</v>
+      </c>
+      <c r="G2697" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70528,7 +70528,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B2699" t="n">
-        <v>4862821</v>
+        <v>4879100</v>
       </c>
       <c r="C2699" t="n">
         <v>388.25</v>
@@ -70537,7 +70537,7 @@
         <v>373.779998779297</v>
       </c>
       <c r="E2699" t="n">
-        <v>385.299987792969</v>
+        <v>387.940002441406</v>
       </c>
       <c r="F2699" t="n">
         <v>374.739990234375</v>
@@ -70546,6 +70546,32 @@
         <v>374.739990234375</v>
       </c>
       <c r="H2699" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>5990534</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>367.267791748047</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>370.269989013672</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>392.089996337891</v>
+      </c>
+      <c r="G2700" t="n">
+        <v>392.089996337891</v>
+      </c>
+      <c r="H2700" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70554,16 +70554,16 @@
         <v>46293.5625</v>
       </c>
       <c r="B2700" t="n">
-        <v>5990534</v>
+        <v>6028100</v>
       </c>
       <c r="C2700" t="n">
         <v>394.5</v>
       </c>
       <c r="D2700" t="n">
-        <v>367.267791748047</v>
+        <v>367.269989013672</v>
       </c>
       <c r="E2700" t="n">
-        <v>370.269989013672</v>
+        <v>370.609985351562</v>
       </c>
       <c r="F2700" t="n">
         <v>392.089996337891</v>
@@ -70572,6 +70572,32 @@
         <v>392.089996337891</v>
       </c>
       <c r="H2700" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B2701" t="n">
+        <v>5086985</v>
+      </c>
+      <c r="C2701" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="D2701" t="n">
+        <v>377.964996337891</v>
+      </c>
+      <c r="E2701" t="n">
+        <v>391</v>
+      </c>
+      <c r="F2701" t="n">
+        <v>388.410003662109</v>
+      </c>
+      <c r="G2701" t="n">
+        <v>388.410003662109</v>
+      </c>
+      <c r="H2701" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70580,16 +70580,16 @@
         <v>46294.5625</v>
       </c>
       <c r="B2701" t="n">
-        <v>5086985</v>
+        <v>5101600</v>
       </c>
       <c r="C2701" t="n">
         <v>391.75</v>
       </c>
       <c r="D2701" t="n">
-        <v>377.964996337891</v>
+        <v>377.799987792969</v>
       </c>
       <c r="E2701" t="n">
-        <v>391</v>
+        <v>390.100006103516</v>
       </c>
       <c r="F2701" t="n">
         <v>388.410003662109</v>
@@ -70598,6 +70598,32 @@
         <v>388.410003662109</v>
       </c>
       <c r="H2701" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>6033488</v>
+      </c>
+      <c r="C2702" t="n">
+        <v>404.687896728516</v>
+      </c>
+      <c r="D2702" t="n">
+        <v>388.890014648438</v>
+      </c>
+      <c r="E2702" t="n">
+        <v>391.670013427734</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>397.309997558594</v>
+      </c>
+      <c r="G2702" t="n">
+        <v>397.309997558594</v>
+      </c>
+      <c r="H2702" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70606,16 +70606,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B2702" t="n">
-        <v>6033488</v>
+        <v>6084900</v>
       </c>
       <c r="C2702" t="n">
-        <v>404.687896728516</v>
+        <v>404.690002441406</v>
       </c>
       <c r="D2702" t="n">
         <v>388.890014648438</v>
       </c>
       <c r="E2702" t="n">
-        <v>391.670013427734</v>
+        <v>391.359985351562</v>
       </c>
       <c r="F2702" t="n">
         <v>397.309997558594</v>
@@ -70624,6 +70624,32 @@
         <v>397.309997558594</v>
       </c>
       <c r="H2702" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B2703" t="n">
+        <v>5258404</v>
+      </c>
+      <c r="C2703" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="D2703" t="n">
+        <v>387.019989013672</v>
+      </c>
+      <c r="E2703" t="n">
+        <v>396.790008544922</v>
+      </c>
+      <c r="F2703" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="G2703" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="H2703" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70632,16 +70632,16 @@
         <v>46296.5625</v>
       </c>
       <c r="B2703" t="n">
-        <v>5258404</v>
+        <v>5309000</v>
       </c>
       <c r="C2703" t="n">
-        <v>398.5</v>
+        <v>398.579986572266</v>
       </c>
       <c r="D2703" t="n">
         <v>387.019989013672</v>
       </c>
       <c r="E2703" t="n">
-        <v>396.790008544922</v>
+        <v>396.010009765625</v>
       </c>
       <c r="F2703" t="n">
         <v>396.25</v>
@@ -70650,6 +70650,32 @@
         <v>396.25</v>
       </c>
       <c r="H2703" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B2704" t="n">
+        <v>4829505</v>
+      </c>
+      <c r="C2704" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="D2704" t="n">
+        <v>400</v>
+      </c>
+      <c r="E2704" t="n">
+        <v>403.440002441406</v>
+      </c>
+      <c r="F2704" t="n">
+        <v>403.239990234375</v>
+      </c>
+      <c r="G2704" t="n">
+        <v>403.239990234375</v>
+      </c>
+      <c r="H2704" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70658,13 +70658,13 @@
         <v>46297.5625</v>
       </c>
       <c r="B2704" t="n">
-        <v>4829505</v>
+        <v>4904700</v>
       </c>
       <c r="C2704" t="n">
         <v>409.5</v>
       </c>
       <c r="D2704" t="n">
-        <v>400</v>
+        <v>399.950012207031</v>
       </c>
       <c r="E2704" t="n">
         <v>403.440002441406</v>
@@ -70676,6 +70676,32 @@
         <v>403.239990234375</v>
       </c>
       <c r="H2704" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B2705" t="n">
+        <v>4446125</v>
+      </c>
+      <c r="C2705" t="n">
+        <v>407.919891357422</v>
+      </c>
+      <c r="D2705" t="n">
+        <v>399.170013427734</v>
+      </c>
+      <c r="E2705" t="n">
+        <v>403.915008544922</v>
+      </c>
+      <c r="F2705" t="n">
+        <v>406.760009765625</v>
+      </c>
+      <c r="G2705" t="n">
+        <v>406.760009765625</v>
+      </c>
+      <c r="H2705" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70684,16 +70684,16 @@
         <v>46300.5625</v>
       </c>
       <c r="B2705" t="n">
-        <v>4446125</v>
+        <v>4449300</v>
       </c>
       <c r="C2705" t="n">
-        <v>407.919891357422</v>
+        <v>407.920013427734</v>
       </c>
       <c r="D2705" t="n">
         <v>399.170013427734</v>
       </c>
       <c r="E2705" t="n">
-        <v>403.915008544922</v>
+        <v>404.420013427734</v>
       </c>
       <c r="F2705" t="n">
         <v>406.760009765625</v>
@@ -70702,6 +70702,32 @@
         <v>406.760009765625</v>
       </c>
       <c r="H2705" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B2706" t="n">
+        <v>5439262</v>
+      </c>
+      <c r="C2706" t="n">
+        <v>432.325012207031</v>
+      </c>
+      <c r="D2706" t="n">
+        <v>412</v>
+      </c>
+      <c r="E2706" t="n">
+        <v>412.910003662109</v>
+      </c>
+      <c r="F2706" t="n">
+        <v>419.910003662109</v>
+      </c>
+      <c r="G2706" t="n">
+        <v>419.910003662109</v>
+      </c>
+      <c r="H2706" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70710,16 +70710,16 @@
         <v>46301.5625</v>
       </c>
       <c r="B2706" t="n">
-        <v>5439262</v>
+        <v>5440700</v>
       </c>
       <c r="C2706" t="n">
-        <v>432.325012207031</v>
+        <v>432.329986572266</v>
       </c>
       <c r="D2706" t="n">
         <v>412</v>
       </c>
       <c r="E2706" t="n">
-        <v>412.910003662109</v>
+        <v>412.799987792969</v>
       </c>
       <c r="F2706" t="n">
         <v>419.910003662109</v>
@@ -70728,6 +70728,32 @@
         <v>419.910003662109</v>
       </c>
       <c r="H2706" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B2707" t="n">
+        <v>3886927</v>
+      </c>
+      <c r="C2707" t="n">
+        <v>416.604888916016</v>
+      </c>
+      <c r="D2707" t="n">
+        <v>404.630889892578</v>
+      </c>
+      <c r="E2707" t="n">
+        <v>413.410003662109</v>
+      </c>
+      <c r="F2707" t="n">
+        <v>405.570007324219</v>
+      </c>
+      <c r="G2707" t="n">
+        <v>405.570007324219</v>
+      </c>
+      <c r="H2707" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70736,13 +70736,13 @@
         <v>46302.5625</v>
       </c>
       <c r="B2707" t="n">
-        <v>3886927</v>
+        <v>3889400</v>
       </c>
       <c r="C2707" t="n">
-        <v>416.604888916016</v>
+        <v>416.600006103516</v>
       </c>
       <c r="D2707" t="n">
-        <v>404.630889892578</v>
+        <v>404.630004882812</v>
       </c>
       <c r="E2707" t="n">
         <v>413.410003662109</v>
@@ -70754,6 +70754,32 @@
         <v>405.570007324219</v>
       </c>
       <c r="H2707" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B2708" t="n">
+        <v>4396131</v>
+      </c>
+      <c r="C2708" t="n">
+        <v>411.889892578125</v>
+      </c>
+      <c r="D2708" t="n">
+        <v>395.799987792969</v>
+      </c>
+      <c r="E2708" t="n">
+        <v>403.690002441406</v>
+      </c>
+      <c r="F2708" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="G2708" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="H2708" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70762,16 +70762,16 @@
         <v>46303.5625</v>
       </c>
       <c r="B2708" t="n">
-        <v>4396131</v>
+        <v>4418600</v>
       </c>
       <c r="C2708" t="n">
-        <v>411.889892578125</v>
+        <v>411.890014648438</v>
       </c>
       <c r="D2708" t="n">
         <v>395.799987792969</v>
       </c>
       <c r="E2708" t="n">
-        <v>403.690002441406</v>
+        <v>402.980010986328</v>
       </c>
       <c r="F2708" t="n">
         <v>398.5</v>
@@ -70780,6 +70780,32 @@
         <v>398.5</v>
       </c>
       <c r="H2708" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B2709" t="n">
+        <v>3832323</v>
+      </c>
+      <c r="C2709" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="D2709" t="n">
+        <v>401.890014648438</v>
+      </c>
+      <c r="E2709" t="n">
+        <v>404.045013427734</v>
+      </c>
+      <c r="F2709" t="n">
+        <v>418.779998779297</v>
+      </c>
+      <c r="G2709" t="n">
+        <v>418.779998779297</v>
+      </c>
+      <c r="H2709" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70788,7 +70788,7 @@
         <v>46304.5625</v>
       </c>
       <c r="B2709" t="n">
-        <v>3832323</v>
+        <v>3834200</v>
       </c>
       <c r="C2709" t="n">
         <v>419.5</v>
@@ -70797,7 +70797,7 @@
         <v>401.890014648438</v>
       </c>
       <c r="E2709" t="n">
-        <v>404.045013427734</v>
+        <v>404.390014648438</v>
       </c>
       <c r="F2709" t="n">
         <v>418.779998779297</v>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70840,16 +70840,16 @@
         <v>46308.5625</v>
       </c>
       <c r="B2711" t="n">
-        <v>3473783</v>
+        <v>3490900</v>
       </c>
       <c r="C2711" t="n">
-        <v>407.804412841797</v>
+        <v>407.799987792969</v>
       </c>
       <c r="D2711" t="n">
         <v>396.040008544922</v>
       </c>
       <c r="E2711" t="n">
-        <v>399</v>
+        <v>397.510009765625</v>
       </c>
       <c r="F2711" t="n">
         <v>397.029998779297</v>
@@ -70858,6 +70858,32 @@
         <v>397.029998779297</v>
       </c>
       <c r="H2711" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B2712" t="n">
+        <v>6847494</v>
+      </c>
+      <c r="C2712" t="n">
+        <v>383.635009765625</v>
+      </c>
+      <c r="D2712" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="E2712" t="n">
+        <v>378.959991455078</v>
+      </c>
+      <c r="F2712" t="n">
+        <v>375.040008544922</v>
+      </c>
+      <c r="G2712" t="n">
+        <v>375.040008544922</v>
+      </c>
+      <c r="H2712" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70866,10 +70866,10 @@
         <v>46309.5625</v>
       </c>
       <c r="B2712" t="n">
-        <v>6847494</v>
+        <v>7157800</v>
       </c>
       <c r="C2712" t="n">
-        <v>383.635009765625</v>
+        <v>383.640014648438</v>
       </c>
       <c r="D2712" t="n">
         <v>370.5</v>
@@ -70884,6 +70884,32 @@
         <v>375.040008544922</v>
       </c>
       <c r="H2712" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B2713" t="n">
+        <v>5323720</v>
+      </c>
+      <c r="C2713" t="n">
+        <v>372.049987792969</v>
+      </c>
+      <c r="D2713" t="n">
+        <v>361.679992675781</v>
+      </c>
+      <c r="E2713" t="n">
+        <v>366.769989013672</v>
+      </c>
+      <c r="F2713" t="n">
+        <v>370.269989013672</v>
+      </c>
+      <c r="G2713" t="n">
+        <v>370.269989013672</v>
+      </c>
+      <c r="H2713" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -70892,7 +70892,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B2713" t="n">
-        <v>5323720</v>
+        <v>5604100</v>
       </c>
       <c r="C2713" t="n">
         <v>372.049987792969</v>
@@ -70901,7 +70901,7 @@
         <v>361.679992675781</v>
       </c>
       <c r="E2713" t="n">
-        <v>366.769989013672</v>
+        <v>367.049987792969</v>
       </c>
       <c r="F2713" t="n">
         <v>370.269989013672</v>
@@ -70910,6 +70910,32 @@
         <v>370.269989013672</v>
       </c>
       <c r="H2713" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B2714" t="n">
+        <v>8742162</v>
+      </c>
+      <c r="C2714" t="n">
+        <v>375.709991455078</v>
+      </c>
+      <c r="D2714" t="n">
+        <v>339.554809570312</v>
+      </c>
+      <c r="E2714" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="F2714" t="n">
+        <v>342</v>
+      </c>
+      <c r="G2714" t="n">
+        <v>342</v>
+      </c>
+      <c r="H2714" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79078,7 +79078,7 @@
         <v>342</v>
       </c>
       <c r="H2714" t="n">
-        <v>8762600</v>
+        <v>8775200</v>
       </c>
       <c r="I2714" t="s">
         <v>9</v>
@@ -79107,9 +79107,38 @@
         <v>346.950012207031</v>
       </c>
       <c r="H2715" t="n">
-        <v>4594369</v>
+        <v>4596400</v>
       </c>
       <c r="I2715" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2716" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C2716" t="n">
+        <v>345</v>
+      </c>
+      <c r="D2716" t="n">
+        <v>346.059997558594</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>340.279998779297</v>
+      </c>
+      <c r="G2716" t="n">
+        <v>340.279998779297</v>
+      </c>
+      <c r="H2716" t="n">
+        <v>4236032</v>
+      </c>
+      <c r="I2716" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79121,7 +79121,7 @@
         <v>46315.5625</v>
       </c>
       <c r="C2716" t="n">
-        <v>345</v>
+        <v>345.279998779297</v>
       </c>
       <c r="D2716" t="n">
         <v>346.059997558594</v>
@@ -79136,9 +79136,38 @@
         <v>340.279998779297</v>
       </c>
       <c r="H2716" t="n">
-        <v>4236032</v>
+        <v>4241200</v>
       </c>
       <c r="I2716" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2717" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C2717" t="n">
+        <v>343.315002441406</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>354.420013427734</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>339.529998779297</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="G2717" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="H2717" t="n">
+        <v>5138227</v>
+      </c>
+      <c r="I2717" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79150,7 +79150,7 @@
         <v>46316.5625</v>
       </c>
       <c r="C2717" t="n">
-        <v>343.315002441406</v>
+        <v>343.440002441406</v>
       </c>
       <c r="D2717" t="n">
         <v>354.420013427734</v>
@@ -79165,9 +79165,38 @@
         <v>347.25</v>
       </c>
       <c r="H2717" t="n">
-        <v>5138227</v>
+        <v>5162500</v>
       </c>
       <c r="I2717" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2718" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>355</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>366.230102539062</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>352.239990234375</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>354.920013427734</v>
+      </c>
+      <c r="G2718" t="n">
+        <v>354.920013427734</v>
+      </c>
+      <c r="H2718" t="n">
+        <v>7309257</v>
+      </c>
+      <c r="I2718" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79179,10 +79179,10 @@
         <v>46317.5625</v>
       </c>
       <c r="C2718" t="n">
-        <v>355</v>
+        <v>356.579986572266</v>
       </c>
       <c r="D2718" t="n">
-        <v>366.230102539062</v>
+        <v>366.230010986328</v>
       </c>
       <c r="E2718" t="n">
         <v>352.239990234375</v>
@@ -79194,9 +79194,38 @@
         <v>354.920013427734</v>
       </c>
       <c r="H2718" t="n">
-        <v>7309257</v>
+        <v>7313000</v>
       </c>
       <c r="I2718" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2719" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>354.299987792969</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>381.450012207031</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>351.240112304688</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>380.549987792969</v>
+      </c>
+      <c r="G2719" t="n">
+        <v>380.549987792969</v>
+      </c>
+      <c r="H2719" t="n">
+        <v>6561456</v>
+      </c>
+      <c r="I2719" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79211,10 +79211,10 @@
         <v>354.299987792969</v>
       </c>
       <c r="D2719" t="n">
-        <v>381.450012207031</v>
+        <v>381.489990234375</v>
       </c>
       <c r="E2719" t="n">
-        <v>351.240112304688</v>
+        <v>351.239990234375</v>
       </c>
       <c r="F2719" t="n">
         <v>380.549987792969</v>
@@ -79223,9 +79223,38 @@
         <v>380.549987792969</v>
       </c>
       <c r="H2719" t="n">
-        <v>6561456</v>
+        <v>6582700</v>
       </c>
       <c r="I2719" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2720" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>384.049987792969</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>394.700012207031</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>379.484100341797</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>390.459991455078</v>
+      </c>
+      <c r="G2720" t="n">
+        <v>390.459991455078</v>
+      </c>
+      <c r="H2720" t="n">
+        <v>5107673</v>
+      </c>
+      <c r="I2720" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79237,13 +79237,13 @@
         <v>46321.5625</v>
       </c>
       <c r="C2720" t="n">
-        <v>384.049987792969</v>
+        <v>384.190002441406</v>
       </c>
       <c r="D2720" t="n">
         <v>394.700012207031</v>
       </c>
       <c r="E2720" t="n">
-        <v>379.484100341797</v>
+        <v>379.480010986328</v>
       </c>
       <c r="F2720" t="n">
         <v>390.459991455078</v>
@@ -79252,9 +79252,38 @@
         <v>390.459991455078</v>
       </c>
       <c r="H2720" t="n">
-        <v>5107673</v>
+        <v>5128600</v>
       </c>
       <c r="I2720" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2721" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>390.989990234375</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>404.769409179688</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>401.700012207031</v>
+      </c>
+      <c r="G2721" t="n">
+        <v>401.700012207031</v>
+      </c>
+      <c r="H2721" t="n">
+        <v>4768697</v>
+      </c>
+      <c r="I2721" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79269,7 +79269,7 @@
         <v>390.989990234375</v>
       </c>
       <c r="D2721" t="n">
-        <v>404.769409179688</v>
+        <v>404.769989013672</v>
       </c>
       <c r="E2721" t="n">
         <v>388.25</v>
@@ -79281,9 +79281,38 @@
         <v>401.700012207031</v>
       </c>
       <c r="H2721" t="n">
-        <v>4768697</v>
+        <v>4769900</v>
       </c>
       <c r="I2721" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2722" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>401.709991455078</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>406.880004882812</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>393.519989013672</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>394.489990234375</v>
+      </c>
+      <c r="G2722" t="n">
+        <v>394.489990234375</v>
+      </c>
+      <c r="H2722" t="n">
+        <v>4467558</v>
+      </c>
+      <c r="I2722" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79295,13 +79295,13 @@
         <v>46323.5625</v>
       </c>
       <c r="C2722" t="n">
-        <v>401.709991455078</v>
+        <v>401.600006103516</v>
       </c>
       <c r="D2722" t="n">
         <v>406.880004882812</v>
       </c>
       <c r="E2722" t="n">
-        <v>393.519989013672</v>
+        <v>393.489990234375</v>
       </c>
       <c r="F2722" t="n">
         <v>394.489990234375</v>
@@ -79310,9 +79310,38 @@
         <v>394.489990234375</v>
       </c>
       <c r="H2722" t="n">
-        <v>4467558</v>
+        <v>4575900</v>
       </c>
       <c r="I2722" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2723" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>369.899993896484</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>389.620697021484</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>380.570007324219</v>
+      </c>
+      <c r="G2723" t="n">
+        <v>380.570007324219</v>
+      </c>
+      <c r="H2723" t="n">
+        <v>7347472</v>
+      </c>
+      <c r="I2723" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PANW.xlsx
+++ b/data/PANW.xlsx
@@ -79324,10 +79324,10 @@
         <v>46324.5625</v>
       </c>
       <c r="C2723" t="n">
-        <v>369.899993896484</v>
+        <v>368.829986572266</v>
       </c>
       <c r="D2723" t="n">
-        <v>389.620697021484</v>
+        <v>389.619995117188</v>
       </c>
       <c r="E2723" t="n">
         <v>367.5</v>
@@ -79339,9 +79339,38 @@
         <v>380.570007324219</v>
       </c>
       <c r="H2723" t="n">
-        <v>7347472</v>
+        <v>7384000</v>
       </c>
       <c r="I2723" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2724" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>383.950012207031</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>390</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>360.019989013672</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>365.869995117188</v>
+      </c>
+      <c r="G2724" t="n">
+        <v>365.869995117188</v>
+      </c>
+      <c r="H2724" t="n">
+        <v>7487335</v>
+      </c>
+      <c r="I2724" t="s">
         <v>9</v>
       </c>
     </row>
